--- a/Result/profitability/8040.xlsx
+++ b/Result/profitability/8040.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1175</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>38.785</v>
+        <v>39.70875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08875000000000001</v>
+        <v>-0.01125000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>37.78375</v>
+        <v>38.97625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.003750000000000017</v>
+        <v>0.03874999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>37.3175</v>
+        <v>37.68875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04250000000000002</v>
+        <v>0.01624999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>36.36625</v>
+        <v>36.75375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01250000000000002</v>
+        <v>0.03624999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>35.4225</v>
+        <v>36.04125</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006249999999999978</v>
+        <v>0.05624999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>34.24625</v>
+        <v>34.635</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03374999999999997</v>
+        <v>0.04874999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>32.96125</v>
+        <v>33.17375000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006249999999999978</v>
+        <v>0.006249999999999985</v>
       </c>
       <c r="N9" t="n">
         <v>30.29625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8040</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>236</v>
+      </c>
+      <c r="D75" t="n">
+        <v>130</v>
+      </c>
+      <c r="E75" t="n">
+        <v>105</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="G75" t="n">
+        <v>17</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9230769230769229</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03956248545496854</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.136363636363637</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07457300938176581</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
